--- a/material_comparison_tool/output/comparison/material_radiative_cooling_comparison_all.xlsx
+++ b/material_comparison_tool/output/comparison/material_radiative_cooling_comparison_all.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:Y94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,25 +496,60 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>Daily_HVAC_kWh_per_m2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Floor_Area_m2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Peak_Cooling_Load_kW</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Peak_Heating_Load_kW</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Simulation_Days</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Sampling_Scale</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Raw_Total_Hours</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Raw_Total_Cooling_Energy_kWh</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Raw_Total_Heating_Energy_kWh</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Raw_Total_HVAC_Energy_kWh</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Saving_cooling_energy_MJ_per_m2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Saving_heating_energy_MJ_per_m2</t>
         </is>
@@ -523,17 +558,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Anhui Province</t>
+          <t>Af</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>基准</t>
+          <t>对比基准</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>默认材料参数，用作对比基线</t>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -555,47 +590,68 @@
         <v>0.2</v>
       </c>
       <c r="J2" t="n">
-        <v>10931.36306429976</v>
+        <v>5608.51972547717</v>
       </c>
       <c r="K2" t="n">
-        <v>171.6610545615817</v>
+        <v>201.9067101171781</v>
       </c>
       <c r="L2" t="n">
-        <v>221.8680157532098</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>393.5290703147915</v>
+        <v>201.9067101171781</v>
       </c>
       <c r="N2" t="n">
-        <v>100</v>
+        <v>0.4647944523876107</v>
       </c>
       <c r="O2" t="n">
-        <v>3.215623645959379</v>
+        <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>1.945116682035099</v>
+        <v>2.35077835790007</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5608.51972547717</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>5608.51972547717</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Anhui Province</t>
+          <t>Af</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>（高反射+高发射）</t>
+          <t>辐射制冷</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>α=0.1, ε=0.95（辐射制冷友好）；</t>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -617,47 +673,68 @@
         <v>0.2</v>
       </c>
       <c r="J3" t="n">
-        <v>9537.001781854282</v>
+        <v>4850.344437563116</v>
       </c>
       <c r="K3" t="n">
-        <v>87.50600183327553</v>
+        <v>174.6123997522722</v>
       </c>
       <c r="L3" t="n">
-        <v>255.8260623134786</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>343.3320641467541</v>
+        <v>174.6123997522722</v>
       </c>
       <c r="N3" t="n">
-        <v>100</v>
+        <v>0.401962246206888</v>
       </c>
       <c r="O3" t="n">
-        <v>1.39051195995594</v>
+        <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>1.948211010693769</v>
+        <v>1.39654900783738</v>
       </c>
       <c r="Q3" t="n">
-        <v>84.15505272830619</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-33.95804656026885</v>
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4850.344437563116</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>4850.344437563116</v>
+      </c>
+      <c r="X3" t="n">
+        <v>81.88293109471778</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Anhui Province</t>
+          <t>Af</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>（高吸收+高发射）</t>
+          <t>辐射制热/保温</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>α=0.9, ε=0.95（辐射制热）；墙体不变</t>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -679,31 +756,7522 @@
         <v>0.2</v>
       </c>
       <c r="J4" t="n">
-        <v>12065.35363015229</v>
+        <v>6021.402310767064</v>
       </c>
       <c r="K4" t="n">
-        <v>220.2505321085814</v>
+        <v>216.7704831876143</v>
       </c>
       <c r="L4" t="n">
-        <v>214.102198576901</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>434.3527306854824</v>
+        <v>216.7704831876143</v>
       </c>
       <c r="N4" t="n">
-        <v>100</v>
+        <v>0.4990112412237898</v>
       </c>
       <c r="O4" t="n">
-        <v>3.303548143522514</v>
+        <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>1.948211010693769</v>
+        <v>2.793608248781913</v>
       </c>
       <c r="Q4" t="n">
-        <v>-48.58947754699966</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>7.765817176308758</v>
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6021.402310767064</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>6021.402310767064</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-44.59131921130859</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Am</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3659.822820141238</v>
+      </c>
+      <c r="K5" t="n">
+        <v>131.5034075381043</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.2502139869803286</v>
+      </c>
+      <c r="M5" t="n">
+        <v>131.7536215250846</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.3033002337133623</v>
+      </c>
+      <c r="O5" t="n">
+        <v>100</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.99168549836581</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.6496459128872127</v>
+      </c>
+      <c r="R5" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3652.872431614007</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6.95038852723135</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3659.822820141238</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Am</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3017.289938762364</v>
+      </c>
+      <c r="K6" t="n">
+        <v>108.3704642442335</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.2519735512115867</v>
+      </c>
+      <c r="M6" t="n">
+        <v>108.6224377954451</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.2500516523836214</v>
+      </c>
+      <c r="O6" t="n">
+        <v>100</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.255742845376307</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.6514300898347951</v>
+      </c>
+      <c r="R6" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3010.290673450932</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6.999265311432962</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3017.289938762364</v>
+      </c>
+      <c r="X6" t="n">
+        <v>69.39882988161217</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.005278692693774178</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Am</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4032.962912222337</v>
+      </c>
+      <c r="K7" t="n">
+        <v>144.9346912887926</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2519735512115867</v>
+      </c>
+      <c r="M7" t="n">
+        <v>145.1866648400041</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.3342234457642821</v>
+      </c>
+      <c r="O7" t="n">
+        <v>100</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.328693030786941</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.6514300898347951</v>
+      </c>
+      <c r="R7" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4025.963646910905</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6.999265311432962</v>
+      </c>
+      <c r="W7" t="n">
+        <v>4032.962912222337</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-40.29385125206497</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0.005278692693774178</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>As</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3759.643403999548</v>
+      </c>
+      <c r="K8" t="n">
+        <v>135.3471625439837</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>135.3471625439837</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.3115726577900177</v>
+      </c>
+      <c r="O8" t="n">
+        <v>100</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.678301259584268</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3759.643403999548</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3759.643403999548</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>As</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2624.072305395571</v>
+      </c>
+      <c r="K9" t="n">
+        <v>94.46660299424056</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>94.46660299424056</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.2174645556957656</v>
+      </c>
+      <c r="O9" t="n">
+        <v>100</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.215642376267439</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2624.072305395571</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2624.072305395571</v>
+      </c>
+      <c r="X9" t="n">
+        <v>122.6416786492295</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>As</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4393.2981495999</v>
+      </c>
+      <c r="K10" t="n">
+        <v>158.1587333855964</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>158.1587333855964</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.3640854820110415</v>
+      </c>
+      <c r="O10" t="n">
+        <v>100</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.281148006302766</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4393.2981495999</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>4393.2981495999</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-68.43471252483803</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Aw</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5826.849524207708</v>
+      </c>
+      <c r="K11" t="n">
+        <v>209.7665828714775</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>209.7665828714775</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.4828880821166608</v>
+      </c>
+      <c r="O11" t="n">
+        <v>100</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.441243896556521</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5826.849524207708</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>5826.849524207708</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Aw</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4910.483258756181</v>
+      </c>
+      <c r="K12" t="n">
+        <v>176.7773973152225</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>176.7773973152225</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.4069461264162581</v>
+      </c>
+      <c r="O12" t="n">
+        <v>100</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.86891212285953</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4910.483258756181</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>4910.483258756181</v>
+      </c>
+      <c r="X12" t="n">
+        <v>98.96755666876481</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Aw</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6279.863942386179</v>
+      </c>
+      <c r="K13" t="n">
+        <v>226.0751019259025</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>226.0751019259025</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.5204307134574181</v>
+      </c>
+      <c r="O13" t="n">
+        <v>100</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.728871562458821</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6279.863942386179</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>6279.863942386179</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-48.92555716327493</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Bsh</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3703.037489837702</v>
+      </c>
+      <c r="K14" t="n">
+        <v>133.3093496341573</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>133.3093496341573</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3068815599313012</v>
+      </c>
+      <c r="O14" t="n">
+        <v>100</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.025686064553095</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3703.037489837702</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3703.037489837702</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Bsh</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3060.765550400871</v>
+      </c>
+      <c r="K15" t="n">
+        <v>110.1875598144314</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>110.1875598144314</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.2536546036243816</v>
+      </c>
+      <c r="O15" t="n">
+        <v>100</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.119600868338073</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3060.765550400871</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3060.765550400871</v>
+      </c>
+      <c r="X15" t="n">
+        <v>69.36536945917767</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Bsh</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4075.026181945102</v>
+      </c>
+      <c r="K16" t="n">
+        <v>146.7009425500237</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>146.7009425500237</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.3377093520948979</v>
+      </c>
+      <c r="O16" t="n">
+        <v>100</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.323341249937722</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4075.026181945102</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>4075.026181945102</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-40.17477874759928</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bsk</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6151.710760599499</v>
+      </c>
+      <c r="K17" t="n">
+        <v>52.60342534064063</v>
+      </c>
+      <c r="L17" t="n">
+        <v>168.8581620409413</v>
+      </c>
+      <c r="M17" t="n">
+        <v>221.4615873815819</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.5098102840275828</v>
+      </c>
+      <c r="O17" t="n">
+        <v>100</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3.125954739333812</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.060799875989337</v>
+      </c>
+      <c r="R17" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1461.20625946224</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4690.504501137259</v>
+      </c>
+      <c r="W17" t="n">
+        <v>6151.710760599499</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Bsk</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5908.513697641592</v>
+      </c>
+      <c r="K18" t="n">
+        <v>19.26399241279131</v>
+      </c>
+      <c r="L18" t="n">
+        <v>193.442500702306</v>
+      </c>
+      <c r="M18" t="n">
+        <v>212.7064931150973</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.4896558312962645</v>
+      </c>
+      <c r="O18" t="n">
+        <v>100</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.424192084505025</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.066570106859542</v>
+      </c>
+      <c r="R18" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U18" t="n">
+        <v>535.110900355314</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5373.402797286279</v>
+      </c>
+      <c r="W18" t="n">
+        <v>5908.513697641592</v>
+      </c>
+      <c r="X18" t="n">
+        <v>100.018298783548</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-73.75301598409413</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Bsk</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6472.264461461942</v>
+      </c>
+      <c r="K19" t="n">
+        <v>71.27342794210286</v>
+      </c>
+      <c r="L19" t="n">
+        <v>161.7280926705271</v>
+      </c>
+      <c r="M19" t="n">
+        <v>233.0015206126299</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.536375507855962</v>
+      </c>
+      <c r="O19" t="n">
+        <v>100</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.266015782082941</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.066570106859542</v>
+      </c>
+      <c r="R19" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1979.81744283619</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4492.447018625752</v>
+      </c>
+      <c r="W19" t="n">
+        <v>6472.264461461942</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-56.01000780438667</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>21.39020811124274</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Bwh</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2739.616102481198</v>
+      </c>
+      <c r="K20" t="n">
+        <v>97.08519593674684</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.540983752576296</v>
+      </c>
+      <c r="M20" t="n">
+        <v>98.62617968932314</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.2270400084929169</v>
+      </c>
+      <c r="O20" t="n">
+        <v>100</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.549188004770664</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.474377923138918</v>
+      </c>
+      <c r="R20" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2696.810998242968</v>
+      </c>
+      <c r="V20" t="n">
+        <v>42.80510423823044</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2739.616102481198</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Bwh</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2000.470934248454</v>
+      </c>
+      <c r="K21" t="n">
+        <v>70.45019442022942</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.566759212714924</v>
+      </c>
+      <c r="M21" t="n">
+        <v>72.01695363294435</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.1657848840537393</v>
+      </c>
+      <c r="O21" t="n">
+        <v>100</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.057062052618101</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.4770420774425661</v>
+      </c>
+      <c r="R21" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1956.949845006373</v>
+      </c>
+      <c r="V21" t="n">
+        <v>43.52108924208121</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2000.470934248454</v>
+      </c>
+      <c r="X21" t="n">
+        <v>79.90500454955226</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.07732638041588324</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Bwh</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3147.384827501732</v>
+      </c>
+      <c r="K22" t="n">
+        <v>111.7390945773474</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.566759212714924</v>
+      </c>
+      <c r="M22" t="n">
+        <v>113.3058537900624</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.2608329967542872</v>
+      </c>
+      <c r="O22" t="n">
+        <v>100</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.790850837468409</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.4770420774425661</v>
+      </c>
+      <c r="R22" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3103.863738259651</v>
+      </c>
+      <c r="V22" t="n">
+        <v>43.52108924208121</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3147.384827501732</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-43.96169592180176</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-0.07732638041588324</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bwk</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>9296.783904365275</v>
+      </c>
+      <c r="K23" t="n">
+        <v>105.0104570931797</v>
+      </c>
+      <c r="L23" t="n">
+        <v>229.6737634639702</v>
+      </c>
+      <c r="M23" t="n">
+        <v>334.6842205571499</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.7704517047816526</v>
+      </c>
+      <c r="O23" t="n">
+        <v>100</v>
+      </c>
+      <c r="P23" t="n">
+        <v>3.541291105911823</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.209206093358269</v>
+      </c>
+      <c r="R23" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2916.957141477214</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6379.826762888062</v>
+      </c>
+      <c r="W23" t="n">
+        <v>9296.783904365275</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Bwk</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>8816.391631508652</v>
+      </c>
+      <c r="K24" t="n">
+        <v>53.69814100546873</v>
+      </c>
+      <c r="L24" t="n">
+        <v>263.6919577288427</v>
+      </c>
+      <c r="M24" t="n">
+        <v>317.3900987343115</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.7306401904565181</v>
+      </c>
+      <c r="O24" t="n">
+        <v>100</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.107523988594457</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.21494818451783</v>
+      </c>
+      <c r="R24" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1491.615027929687</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7324.776603578965</v>
+      </c>
+      <c r="W24" t="n">
+        <v>8816.391631508652</v>
+      </c>
+      <c r="X24" t="n">
+        <v>153.9369482631328</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>-102.0545827946175</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Bwk</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>9634.696174384884</v>
+      </c>
+      <c r="K25" t="n">
+        <v>124.6114777351891</v>
+      </c>
+      <c r="L25" t="n">
+        <v>222.2375845426667</v>
+      </c>
+      <c r="M25" t="n">
+        <v>346.8490622778559</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.7984554840650456</v>
+      </c>
+      <c r="O25" t="n">
+        <v>100</v>
+      </c>
+      <c r="P25" t="n">
+        <v>3.588921023140119</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.21494818451783</v>
+      </c>
+      <c r="R25" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3461.429937088587</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6173.266237296297</v>
+      </c>
+      <c r="W25" t="n">
+        <v>9634.696174384884</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-58.80306192602838</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>22.30853676391061</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cfa</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3075.239271240129</v>
+      </c>
+      <c r="K26" t="n">
+        <v>55.00406681054802</v>
+      </c>
+      <c r="L26" t="n">
+        <v>55.70454695409664</v>
+      </c>
+      <c r="M26" t="n">
+        <v>110.7086137646447</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.2548540832519444</v>
+      </c>
+      <c r="O26" t="n">
+        <v>100</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3.027667150918207</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.054847026643049</v>
+      </c>
+      <c r="R26" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1527.890744737445</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1547.348526502684</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3075.239271240129</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Cfa</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2545.559295208232</v>
+      </c>
+      <c r="K27" t="n">
+        <v>26.54666972689498</v>
+      </c>
+      <c r="L27" t="n">
+        <v>65.09346490060136</v>
+      </c>
+      <c r="M27" t="n">
+        <v>91.64013462749634</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.2109579526415661</v>
+      </c>
+      <c r="O27" t="n">
+        <v>100</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.334681453984062</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.056502070479107</v>
+      </c>
+      <c r="R27" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U27" t="n">
+        <v>737.4074924137495</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1808.151802794482</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2545.559295208232</v>
+      </c>
+      <c r="X27" t="n">
+        <v>85.3721912509591</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>-28.16675383951416</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Cfa</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3519.453821776934</v>
+      </c>
+      <c r="K28" t="n">
+        <v>72.79521454214627</v>
+      </c>
+      <c r="L28" t="n">
+        <v>53.90512304182335</v>
+      </c>
+      <c r="M28" t="n">
+        <v>126.7003375839696</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.2916674437936686</v>
+      </c>
+      <c r="O28" t="n">
+        <v>100</v>
+      </c>
+      <c r="P28" t="n">
+        <v>3.307449652613403</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.056502070479107</v>
+      </c>
+      <c r="R28" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2022.089292837396</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1497.364528939538</v>
+      </c>
+      <c r="W28" t="n">
+        <v>3519.453821776934</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-53.37344319479475</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>5.398271736819872</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Cfb</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>6041.481245363135</v>
+      </c>
+      <c r="K29" t="n">
+        <v>6.408077591709003</v>
+      </c>
+      <c r="L29" t="n">
+        <v>211.0852472413639</v>
+      </c>
+      <c r="M29" t="n">
+        <v>217.4933248330729</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.5006752413284365</v>
+      </c>
+      <c r="O29" t="n">
+        <v>100</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.9621580626220062</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.787524864793315</v>
+      </c>
+      <c r="R29" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U29" t="n">
+        <v>178.0021553252501</v>
+      </c>
+      <c r="V29" t="n">
+        <v>5863.479090037885</v>
+      </c>
+      <c r="W29" t="n">
+        <v>6041.481245363135</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Cfb</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>6409.373354086026</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.039887532400182</v>
+      </c>
+      <c r="L30" t="n">
+        <v>229.6975532146968</v>
+      </c>
+      <c r="M30" t="n">
+        <v>230.7374407470969</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.5311635376314385</v>
+      </c>
+      <c r="O30" t="n">
+        <v>100</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.4652598670508404</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.789853117762785</v>
+      </c>
+      <c r="R30" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U30" t="n">
+        <v>28.88576478889395</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6380.487589297132</v>
+      </c>
+      <c r="W30" t="n">
+        <v>6409.373354086026</v>
+      </c>
+      <c r="X30" t="n">
+        <v>16.10457017792646</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-55.83691791999868</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Cfb</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5989.609653205796</v>
+      </c>
+      <c r="K31" t="n">
+        <v>11.82925350565776</v>
+      </c>
+      <c r="L31" t="n">
+        <v>203.7966940097509</v>
+      </c>
+      <c r="M31" t="n">
+        <v>215.6259475154087</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.4963764905971654</v>
+      </c>
+      <c r="O31" t="n">
+        <v>100</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.387658006451045</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.789853117762785</v>
+      </c>
+      <c r="R31" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U31" t="n">
+        <v>328.5903751571599</v>
+      </c>
+      <c r="V31" t="n">
+        <v>5661.019278048637</v>
+      </c>
+      <c r="W31" t="n">
+        <v>5989.609653205796</v>
+      </c>
+      <c r="X31" t="n">
+        <v>-16.26352774184626</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>21.86565969483885</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Cfc</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>10913.96282452266</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>392.9026616828157</v>
+      </c>
+      <c r="M32" t="n">
+        <v>392.9026616828157</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.9044720572808833</v>
+      </c>
+      <c r="O32" t="n">
+        <v>100</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.220127619245314</v>
+      </c>
+      <c r="R32" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>10913.96282452266</v>
+      </c>
+      <c r="W32" t="n">
+        <v>10913.96282452266</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Cfc</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>11567.3987203102</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>416.4263539311672</v>
+      </c>
+      <c r="M33" t="n">
+        <v>416.4263539311672</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.9586242033406244</v>
+      </c>
+      <c r="O33" t="n">
+        <v>100</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.222539917348942</v>
+      </c>
+      <c r="R33" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>11567.3987203102</v>
+      </c>
+      <c r="W33" t="n">
+        <v>11567.3987203102</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>-70.57107674505448</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Cfc</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>10608.60975173829</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.01187741978941254</v>
+      </c>
+      <c r="L34" t="n">
+        <v>381.898073642789</v>
+      </c>
+      <c r="M34" t="n">
+        <v>381.9099510625784</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.8791665540114603</v>
+      </c>
+      <c r="O34" t="n">
+        <v>100</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.1772139122162298</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.222539917348942</v>
+      </c>
+      <c r="R34" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.3299283274836817</v>
+      </c>
+      <c r="V34" t="n">
+        <v>10608.2798234108</v>
+      </c>
+      <c r="W34" t="n">
+        <v>10608.60975173829</v>
+      </c>
+      <c r="X34" t="n">
+        <v>-0.03563225936823762</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>33.01376412008011</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Csa</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2048.205327319306</v>
+      </c>
+      <c r="K35" t="n">
+        <v>25.81578964773434</v>
+      </c>
+      <c r="L35" t="n">
+        <v>47.91960213576067</v>
+      </c>
+      <c r="M35" t="n">
+        <v>73.735391783495</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.1697407729822629</v>
+      </c>
+      <c r="O35" t="n">
+        <v>100</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.632130654948682</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.028152639899479</v>
+      </c>
+      <c r="R35" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U35" t="n">
+        <v>717.1052679926204</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1331.100059326685</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2048.205327319306</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Csa</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1811.042701905577</v>
+      </c>
+      <c r="K36" t="n">
+        <v>12.52591884993135</v>
+      </c>
+      <c r="L36" t="n">
+        <v>52.67161841866942</v>
+      </c>
+      <c r="M36" t="n">
+        <v>65.19753726860077</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.1500864117601307</v>
+      </c>
+      <c r="O36" t="n">
+        <v>100</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.7709008265961395</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.029987254350204</v>
+      </c>
+      <c r="R36" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U36" t="n">
+        <v>347.9421902758707</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1463.100511629706</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1811.042701905577</v>
+      </c>
+      <c r="X36" t="n">
+        <v>39.86961239340898</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>-14.25604884872627</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Csa</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2282.49962754265</v>
+      </c>
+      <c r="K37" t="n">
+        <v>35.42272959510628</v>
+      </c>
+      <c r="L37" t="n">
+        <v>46.74725699642914</v>
+      </c>
+      <c r="M37" t="n">
+        <v>82.16998659153542</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.1891574276969047</v>
+      </c>
+      <c r="O37" t="n">
+        <v>100</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.890825589801436</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.029987254350204</v>
+      </c>
+      <c r="R37" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U37" t="n">
+        <v>983.9647109751743</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1298.534916567476</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2282.49962754265</v>
+      </c>
+      <c r="X37" t="n">
+        <v>-28.82081984211581</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>3.517035417994578</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Csb</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1193.956587786045</v>
+      </c>
+      <c r="K38" t="n">
+        <v>24.56886231368102</v>
+      </c>
+      <c r="L38" t="n">
+        <v>18.41357484661658</v>
+      </c>
+      <c r="M38" t="n">
+        <v>42.98243716029761</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.0989466785458048</v>
+      </c>
+      <c r="O38" t="n">
+        <v>100</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.884600702427703</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.361936183086099</v>
+      </c>
+      <c r="R38" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U38" t="n">
+        <v>682.4683976022505</v>
+      </c>
+      <c r="V38" t="n">
+        <v>511.4881901837939</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1193.956587786045</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Csb</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J39" t="n">
+        <v>744.390194916539</v>
+      </c>
+      <c r="K39" t="n">
+        <v>7.805659513305914</v>
+      </c>
+      <c r="L39" t="n">
+        <v>18.99238750368949</v>
+      </c>
+      <c r="M39" t="n">
+        <v>26.7980470169954</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.0616897951588292</v>
+      </c>
+      <c r="O39" t="n">
+        <v>100</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.9544740000274339</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.366759099759321</v>
+      </c>
+      <c r="R39" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U39" t="n">
+        <v>216.8238753696087</v>
+      </c>
+      <c r="V39" t="n">
+        <v>527.5663195469303</v>
+      </c>
+      <c r="W39" t="n">
+        <v>744.390194916539</v>
+      </c>
+      <c r="X39" t="n">
+        <v>50.28960840112531</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>-1.736437971218727</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Csb</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1529.798692915075</v>
+      </c>
+      <c r="K40" t="n">
+        <v>36.62673646612787</v>
+      </c>
+      <c r="L40" t="n">
+        <v>18.44601647881482</v>
+      </c>
+      <c r="M40" t="n">
+        <v>55.07275294494269</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.1267788972029067</v>
+      </c>
+      <c r="O40" t="n">
+        <v>100</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.294284389608666</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.366759099759321</v>
+      </c>
+      <c r="R40" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1017.40934628133</v>
+      </c>
+      <c r="V40" t="n">
+        <v>512.389346633745</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1529.798692915075</v>
+      </c>
+      <c r="X40" t="n">
+        <v>-36.17362245734056</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>-0.0973248965947171</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Csc</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J41" t="n">
+        <v>8207.066448142872</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.4940770331697146</v>
+      </c>
+      <c r="L41" t="n">
+        <v>294.9603150999737</v>
+      </c>
+      <c r="M41" t="n">
+        <v>295.4543921331434</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.680143628299133</v>
+      </c>
+      <c r="O41" t="n">
+        <v>100</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.532839028227742</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.858091294193039</v>
+      </c>
+      <c r="R41" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U41" t="n">
+        <v>13.72436203249207</v>
+      </c>
+      <c r="V41" t="n">
+        <v>8193.34208611038</v>
+      </c>
+      <c r="W41" t="n">
+        <v>8207.066448142872</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Csc</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J42" t="n">
+        <v>9195.544359197887</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>331.039596931124</v>
+      </c>
+      <c r="M42" t="n">
+        <v>331.039596931124</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.7620616872263442</v>
+      </c>
+      <c r="O42" t="n">
+        <v>100</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3.868112409151799</v>
+      </c>
+      <c r="R42" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>9195.544359197887</v>
+      </c>
+      <c r="W42" t="n">
+        <v>9195.544359197887</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.482231099509144</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>-108.2378454934509</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Csc</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J43" t="n">
+        <v>7815.862941675567</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.80553350887424</v>
+      </c>
+      <c r="L43" t="n">
+        <v>279.5655323914462</v>
+      </c>
+      <c r="M43" t="n">
+        <v>281.3710659003204</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.6477234482051574</v>
+      </c>
+      <c r="O43" t="n">
+        <v>100</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.8212079181715077</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.868112409151799</v>
+      </c>
+      <c r="R43" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U43" t="n">
+        <v>50.15370857983999</v>
+      </c>
+      <c r="V43" t="n">
+        <v>7765.709233095727</v>
+      </c>
+      <c r="W43" t="n">
+        <v>7815.862941675567</v>
+      </c>
+      <c r="X43" t="n">
+        <v>-3.934369427113576</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>46.18434812558246</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Cwa</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2953.314067502833</v>
+      </c>
+      <c r="K44" t="n">
+        <v>106.2662930070066</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.0530134230953542</v>
+      </c>
+      <c r="M44" t="n">
+        <v>106.319306430102</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.2447497845996823</v>
+      </c>
+      <c r="O44" t="n">
+        <v>100</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.135436601385847</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.1301760637068441</v>
+      </c>
+      <c r="R44" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2951.841472416851</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.472595085982061</v>
+      </c>
+      <c r="W44" t="n">
+        <v>2953.314067502833</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Cwa</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2362.531906478485</v>
+      </c>
+      <c r="K45" t="n">
+        <v>84.99740102449385</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.05374760873161447</v>
+      </c>
+      <c r="M45" t="n">
+        <v>85.05114863322545</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.1957899370009794</v>
+      </c>
+      <c r="O45" t="n">
+        <v>100</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.175118075800393</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.1314843620786826</v>
+      </c>
+      <c r="R45" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2361.038917347051</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.492989131433735</v>
+      </c>
+      <c r="W45" t="n">
+        <v>2362.531906478485</v>
+      </c>
+      <c r="X45" t="n">
+        <v>63.80667594753835</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>-0.002202556908780816</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Cwa</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3292.759287142093</v>
+      </c>
+      <c r="K46" t="n">
+        <v>118.4855867283837</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.05374760873161447</v>
+      </c>
+      <c r="M46" t="n">
+        <v>118.5393343371153</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.2728806039068033</v>
+      </c>
+      <c r="O46" t="n">
+        <v>100</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.566727049985468</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.1314843620786826</v>
+      </c>
+      <c r="R46" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3291.266298010659</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.492989131433735</v>
+      </c>
+      <c r="W46" t="n">
+        <v>3292.759287142093</v>
+      </c>
+      <c r="X46" t="n">
+        <v>-36.6578811641313</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>-0.002202556908780816</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Cwb</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2246.153625729251</v>
+      </c>
+      <c r="K47" t="n">
+        <v>47.00233674658153</v>
+      </c>
+      <c r="L47" t="n">
+        <v>33.85919377967149</v>
+      </c>
+      <c r="M47" t="n">
+        <v>80.86153052625302</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.1861453280991092</v>
+      </c>
+      <c r="O47" t="n">
+        <v>100</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.77377757819534</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.526241646402304</v>
+      </c>
+      <c r="R47" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1305.62046518282</v>
+      </c>
+      <c r="V47" t="n">
+        <v>940.5331605464304</v>
+      </c>
+      <c r="W47" t="n">
+        <v>2246.153625729251</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Cwb</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1268.789271313765</v>
+      </c>
+      <c r="K48" t="n">
+        <v>6.863134791307045</v>
+      </c>
+      <c r="L48" t="n">
+        <v>38.81327897598851</v>
+      </c>
+      <c r="M48" t="n">
+        <v>45.67641376729555</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.1051482821530745</v>
+      </c>
+      <c r="O48" t="n">
+        <v>100</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.6511514509696081</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1.531967713780866</v>
+      </c>
+      <c r="R48" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U48" t="n">
+        <v>190.6426330918624</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1078.146638221903</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1268.789271313765</v>
+      </c>
+      <c r="X48" t="n">
+        <v>120.4176058658235</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>-14.86225558895105</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Cwb</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2946.0851030761</v>
+      </c>
+      <c r="K49" t="n">
+        <v>73.35193725445954</v>
+      </c>
+      <c r="L49" t="n">
+        <v>32.70712645628007</v>
+      </c>
+      <c r="M49" t="n">
+        <v>106.0590637107396</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.2441506991499531</v>
+      </c>
+      <c r="O49" t="n">
+        <v>100</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.946970636801375</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.531967713780866</v>
+      </c>
+      <c r="R49" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2037.553812623876</v>
+      </c>
+      <c r="V49" t="n">
+        <v>908.5312904522242</v>
+      </c>
+      <c r="W49" t="n">
+        <v>2946.0851030761</v>
+      </c>
+      <c r="X49" t="n">
+        <v>-79.04880152363403</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>3.456201970174263</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Cwc</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J50" t="n">
+        <v>5628.652863449024</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.863590896151269</v>
+      </c>
+      <c r="L50" t="n">
+        <v>201.7679121880136</v>
+      </c>
+      <c r="M50" t="n">
+        <v>202.6315030841649</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.4664629444847258</v>
+      </c>
+      <c r="O50" t="n">
+        <v>100</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.5942432920471148</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.375642388468045</v>
+      </c>
+      <c r="R50" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U50" t="n">
+        <v>23.98863600420192</v>
+      </c>
+      <c r="V50" t="n">
+        <v>5604.664227444822</v>
+      </c>
+      <c r="W50" t="n">
+        <v>5628.652863449024</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Cwc</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J51" t="n">
+        <v>6488.465420021903</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>233.5847551207885</v>
+      </c>
+      <c r="M51" t="n">
+        <v>233.5847551207885</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.5377181287310969</v>
+      </c>
+      <c r="O51" t="n">
+        <v>100</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2.382874488394404</v>
+      </c>
+      <c r="R51" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>6488.465420021903</v>
+      </c>
+      <c r="W51" t="n">
+        <v>6488.465420021903</v>
+      </c>
+      <c r="X51" t="n">
+        <v>2.590772688453807</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>-95.45052879832471</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Cwc</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J52" t="n">
+        <v>5665.434728385281</v>
+      </c>
+      <c r="K52" t="n">
+        <v>5.844804112699417</v>
+      </c>
+      <c r="L52" t="n">
+        <v>198.1108461091707</v>
+      </c>
+      <c r="M52" t="n">
+        <v>203.9556502218701</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.4695111653357968</v>
+      </c>
+      <c r="O52" t="n">
+        <v>100</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1.026732985649335</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2.382874488394404</v>
+      </c>
+      <c r="R52" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U52" t="n">
+        <v>162.355669797206</v>
+      </c>
+      <c r="V52" t="n">
+        <v>5503.079058588075</v>
+      </c>
+      <c r="W52" t="n">
+        <v>5665.434728385281</v>
+      </c>
+      <c r="X52" t="n">
+        <v>-14.94363964964444</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>10.97119823652875</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Dfa</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J53" t="n">
+        <v>8745.219752737761</v>
+      </c>
+      <c r="K53" t="n">
+        <v>13.51324178169158</v>
+      </c>
+      <c r="L53" t="n">
+        <v>301.3146693168678</v>
+      </c>
+      <c r="M53" t="n">
+        <v>314.8279110985594</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.7247419684589305</v>
+      </c>
+      <c r="O53" t="n">
+        <v>100</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1.452614819405729</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>4.731472054367636</v>
+      </c>
+      <c r="R53" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U53" t="n">
+        <v>375.3678272692105</v>
+      </c>
+      <c r="V53" t="n">
+        <v>8369.851925468551</v>
+      </c>
+      <c r="W53" t="n">
+        <v>8745.219752737761</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Dfa</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J54" t="n">
+        <v>9074.401383874128</v>
+      </c>
+      <c r="K54" t="n">
+        <v>6.014258367085843</v>
+      </c>
+      <c r="L54" t="n">
+        <v>320.6641914523827</v>
+      </c>
+      <c r="M54" t="n">
+        <v>326.6784498194686</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.7520222141332151</v>
+      </c>
+      <c r="O54" t="n">
+        <v>100</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1.026671468881837</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>4.734310576900605</v>
+      </c>
+      <c r="R54" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U54" t="n">
+        <v>167.0627324190512</v>
+      </c>
+      <c r="V54" t="n">
+        <v>8907.338651455077</v>
+      </c>
+      <c r="W54" t="n">
+        <v>9074.401383874128</v>
+      </c>
+      <c r="X54" t="n">
+        <v>22.4969502438172</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>-58.04856640654475</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Dfa</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J55" t="n">
+        <v>8657.719025800108</v>
+      </c>
+      <c r="K55" t="n">
+        <v>19.34126620183834</v>
+      </c>
+      <c r="L55" t="n">
+        <v>292.3366187269656</v>
+      </c>
+      <c r="M55" t="n">
+        <v>311.6778849288039</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.7174905270000089</v>
+      </c>
+      <c r="O55" t="n">
+        <v>100</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1.700409138831067</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>4.734310576900605</v>
+      </c>
+      <c r="R55" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U55" t="n">
+        <v>537.2573944955095</v>
+      </c>
+      <c r="V55" t="n">
+        <v>8120.461631304599</v>
+      </c>
+      <c r="W55" t="n">
+        <v>8657.719025800108</v>
+      </c>
+      <c r="X55" t="n">
+        <v>-17.4840732604403</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>26.93415176970672</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dfb</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J56" t="n">
+        <v>14023.80652486679</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3.823779724199179</v>
+      </c>
+      <c r="L56" t="n">
+        <v>501.0332551710052</v>
+      </c>
+      <c r="M56" t="n">
+        <v>504.8570348952044</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1.162193910900563</v>
+      </c>
+      <c r="O56" t="n">
+        <v>100</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1.013122548415558</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>4.951313094705162</v>
+      </c>
+      <c r="R56" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U56" t="n">
+        <v>106.2161034499772</v>
+      </c>
+      <c r="V56" t="n">
+        <v>13917.59042141681</v>
+      </c>
+      <c r="W56" t="n">
+        <v>14023.80652486679</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Dfb</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J57" t="n">
+        <v>14602.03485143005</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.2148211600103119</v>
+      </c>
+      <c r="L57" t="n">
+        <v>525.4584334914716</v>
+      </c>
+      <c r="M57" t="n">
+        <v>525.6732546514819</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1.210113385477629</v>
+      </c>
+      <c r="O57" t="n">
+        <v>100</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.2808634493986029</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>4.956516970261085</v>
+      </c>
+      <c r="R57" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U57" t="n">
+        <v>5.967254444730887</v>
+      </c>
+      <c r="V57" t="n">
+        <v>14596.06759698532</v>
+      </c>
+      <c r="W57" t="n">
+        <v>14602.03485143005</v>
+      </c>
+      <c r="X57" t="n">
+        <v>10.8268756925666</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>-73.27553496139916</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Dfb</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J58" t="n">
+        <v>13875.22799364014</v>
+      </c>
+      <c r="K58" t="n">
+        <v>8.304762810230427</v>
+      </c>
+      <c r="L58" t="n">
+        <v>491.2034449608145</v>
+      </c>
+      <c r="M58" t="n">
+        <v>499.508207771045</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1.149880772953602</v>
+      </c>
+      <c r="O58" t="n">
+        <v>100</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1.396575281338461</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>4.956516970261085</v>
+      </c>
+      <c r="R58" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U58" t="n">
+        <v>230.6878558397341</v>
+      </c>
+      <c r="V58" t="n">
+        <v>13644.5401378004</v>
+      </c>
+      <c r="W58" t="n">
+        <v>13875.22799364014</v>
+      </c>
+      <c r="X58" t="n">
+        <v>-13.44294925809374</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>29.48943063057214</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Dfc</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J59" t="n">
+        <v>29069.4675587254</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.3047733134746101</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1046.19605880064</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1046.500832114114</v>
+      </c>
+      <c r="N59" t="n">
+        <v>2.409071897131939</v>
+      </c>
+      <c r="O59" t="n">
+        <v>100</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.7123954092717336</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>8.237375638805208</v>
+      </c>
+      <c r="R59" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U59" t="n">
+        <v>8.465925374294724</v>
+      </c>
+      <c r="V59" t="n">
+        <v>29061.00163335111</v>
+      </c>
+      <c r="W59" t="n">
+        <v>29069.4675587254</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Dfc</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J60" t="n">
+        <v>30087.17359844529</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1083.13824954403</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1083.13824954403</v>
+      </c>
+      <c r="N60" t="n">
+        <v>2.493412176666737</v>
+      </c>
+      <c r="O60" t="n">
+        <v>100</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>8.245823841964055</v>
+      </c>
+      <c r="R60" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>30087.17359844529</v>
+      </c>
+      <c r="W60" t="n">
+        <v>30087.17359844529</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0.9143199404238302</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>-110.8265722301721</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Dfc</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J61" t="n">
+        <v>28640.50917546556</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1.390799201595196</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1029.667531115165</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1031.05833031676</v>
+      </c>
+      <c r="N61" t="n">
+        <v>2.373522859845212</v>
+      </c>
+      <c r="O61" t="n">
+        <v>100</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1.144339139632447</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>8.245823841964055</v>
+      </c>
+      <c r="R61" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U61" t="n">
+        <v>38.63331115542212</v>
+      </c>
+      <c r="V61" t="n">
+        <v>28601.87586431014</v>
+      </c>
+      <c r="W61" t="n">
+        <v>28640.50917546556</v>
+      </c>
+      <c r="X61" t="n">
+        <v>-3.258077664361759</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>49.58558305642487</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Dfd</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J62" t="n">
+        <v>37769.85517130328</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.1614945086494414</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1359.553291658269</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1359.714786166918</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3.130098494859388</v>
+      </c>
+      <c r="O62" t="n">
+        <v>100</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.3242231788765524</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>9.022872583914294</v>
+      </c>
+      <c r="R62" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U62" t="n">
+        <v>4.485958573595593</v>
+      </c>
+      <c r="V62" t="n">
+        <v>37765.36921272968</v>
+      </c>
+      <c r="W62" t="n">
+        <v>37769.85517130328</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Dfd</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J63" t="n">
+        <v>38851.43050887697</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1398.651498319571</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1398.651498319571</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3.219731810127926</v>
+      </c>
+      <c r="O63" t="n">
+        <v>100</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>9.022872583914294</v>
+      </c>
+      <c r="R63" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>38851.43050887697</v>
+      </c>
+      <c r="W63" t="n">
+        <v>38851.43050887697</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0.4844835259483241</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>-117.2946199839064</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Dfd</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J64" t="n">
+        <v>37311.14830930718</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1.651000332028769</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1341.55033880303</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1343.201339135059</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3.092084114030982</v>
+      </c>
+      <c r="O64" t="n">
+        <v>100</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.7582355859331014</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>9.022872583914294</v>
+      </c>
+      <c r="R64" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U64" t="n">
+        <v>45.86112033413248</v>
+      </c>
+      <c r="V64" t="n">
+        <v>37265.28718897304</v>
+      </c>
+      <c r="W64" t="n">
+        <v>37311.14830930718</v>
+      </c>
+      <c r="X64" t="n">
+        <v>-4.468517470137984</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>54.00885856571722</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Dsa</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J65" t="n">
+        <v>6570.057880770521</v>
+      </c>
+      <c r="K65" t="n">
+        <v>24.74363532608513</v>
+      </c>
+      <c r="L65" t="n">
+        <v>211.7784483816536</v>
+      </c>
+      <c r="M65" t="n">
+        <v>236.5220837077388</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.5444799348704852</v>
+      </c>
+      <c r="O65" t="n">
+        <v>100</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1.923215331136066</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>2.992748150225498</v>
+      </c>
+      <c r="R65" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U65" t="n">
+        <v>687.3232035023647</v>
+      </c>
+      <c r="V65" t="n">
+        <v>5882.734677268157</v>
+      </c>
+      <c r="W65" t="n">
+        <v>6570.057880770521</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Dsa</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J66" t="n">
+        <v>6730.354926646675</v>
+      </c>
+      <c r="K66" t="n">
+        <v>11.60081602635811</v>
+      </c>
+      <c r="L66" t="n">
+        <v>230.6919613329222</v>
+      </c>
+      <c r="M66" t="n">
+        <v>242.2927773592803</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.5577642204403321</v>
+      </c>
+      <c r="O66" t="n">
+        <v>100</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1.145035285585866</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>2.996158157379869</v>
+      </c>
+      <c r="R66" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U66" t="n">
+        <v>322.2448896210586</v>
+      </c>
+      <c r="V66" t="n">
+        <v>6408.110037025616</v>
+      </c>
+      <c r="W66" t="n">
+        <v>6730.354926646675</v>
+      </c>
+      <c r="X66" t="n">
+        <v>39.42845789918105</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>-56.74053885380559</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Dsa</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J67" t="n">
+        <v>6617.594824809173</v>
+      </c>
+      <c r="K67" t="n">
+        <v>33.95554252151585</v>
+      </c>
+      <c r="L67" t="n">
+        <v>204.2778711716144</v>
+      </c>
+      <c r="M67" t="n">
+        <v>238.2334136931302</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.5484194606195447</v>
+      </c>
+      <c r="O67" t="n">
+        <v>100</v>
+      </c>
+      <c r="P67" t="n">
+        <v>2.3117297948329</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>2.996158157379869</v>
+      </c>
+      <c r="R67" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U67" t="n">
+        <v>943.2095144865514</v>
+      </c>
+      <c r="V67" t="n">
+        <v>5674.385310322621</v>
+      </c>
+      <c r="W67" t="n">
+        <v>6617.594824809173</v>
+      </c>
+      <c r="X67" t="n">
+        <v>-27.63572158629218</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>22.50173163011789</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Dsb</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J68" t="n">
+        <v>6221.35988724351</v>
+      </c>
+      <c r="K68" t="n">
+        <v>223.9689559407664</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>223.9689559407664</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.5155823110975285</v>
+      </c>
+      <c r="O68" t="n">
+        <v>100</v>
+      </c>
+      <c r="P68" t="n">
+        <v>2.663817534905117</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U68" t="n">
+        <v>6221.35988724351</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>6221.35988724351</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Dsb</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J69" t="n">
+        <v>5375.491702099187</v>
+      </c>
+      <c r="K69" t="n">
+        <v>193.5177012755707</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>193.5177012755707</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.4454827377430265</v>
+      </c>
+      <c r="O69" t="n">
+        <v>100</v>
+      </c>
+      <c r="P69" t="n">
+        <v>2.154453138764569</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U69" t="n">
+        <v>5375.491702099187</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>5375.491702099187</v>
+      </c>
+      <c r="X69" t="n">
+        <v>91.35376399558703</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Dsb</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J70" t="n">
+        <v>6630.712546284294</v>
+      </c>
+      <c r="K70" t="n">
+        <v>238.7056516662346</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>238.7056516662346</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.5495065646091956</v>
+      </c>
+      <c r="O70" t="n">
+        <v>100</v>
+      </c>
+      <c r="P70" t="n">
+        <v>3.016767927444396</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U70" t="n">
+        <v>6630.712546284294</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>6630.712546284294</v>
+      </c>
+      <c r="X70" t="n">
+        <v>-44.21008717640458</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Dsc</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J71" t="n">
+        <v>18130.05093384202</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.1552728647889307</v>
+      </c>
+      <c r="L71" t="n">
+        <v>652.5265607535238</v>
+      </c>
+      <c r="M71" t="n">
+        <v>652.6818336183128</v>
+      </c>
+      <c r="N71" t="n">
+        <v>1.502490408881935</v>
+      </c>
+      <c r="O71" t="n">
+        <v>100</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.3666124758834151</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>5.269533175622027</v>
+      </c>
+      <c r="R71" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U71" t="n">
+        <v>4.313135133025852</v>
+      </c>
+      <c r="V71" t="n">
+        <v>18125.73779870899</v>
+      </c>
+      <c r="W71" t="n">
+        <v>18130.05093384202</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Dsc</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J72" t="n">
+        <v>18967.12303872579</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>682.8164293941285</v>
+      </c>
+      <c r="M72" t="n">
+        <v>682.8164293941285</v>
+      </c>
+      <c r="N72" t="n">
+        <v>1.571861025308767</v>
+      </c>
+      <c r="O72" t="n">
+        <v>100</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>5.275824347774859</v>
+      </c>
+      <c r="R72" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>18967.12303872579</v>
+      </c>
+      <c r="W72" t="n">
+        <v>18967.12303872579</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0.4658185943667921</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>-90.86960592181413</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Dsc</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J73" t="n">
+        <v>17785.43540567013</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.9844389593308328</v>
+      </c>
+      <c r="L73" t="n">
+        <v>639.2912356447939</v>
+      </c>
+      <c r="M73" t="n">
+        <v>640.2756746041247</v>
+      </c>
+      <c r="N73" t="n">
+        <v>1.473931110967138</v>
+      </c>
+      <c r="O73" t="n">
+        <v>100</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.712828033945099</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>5.275824347774859</v>
+      </c>
+      <c r="R73" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U73" t="n">
+        <v>27.34552664807869</v>
+      </c>
+      <c r="V73" t="n">
+        <v>17758.08987902205</v>
+      </c>
+      <c r="W73" t="n">
+        <v>17785.43540567013</v>
+      </c>
+      <c r="X73" t="n">
+        <v>-2.487498283625706</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>39.70597532618956</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Dsd</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J74" t="n">
+        <v>44208.6249245576</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.01092246766777597</v>
+      </c>
+      <c r="L74" t="n">
+        <v>1591.499574816406</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1591.510497284074</v>
+      </c>
+      <c r="N74" t="n">
+        <v>3.663698198167757</v>
+      </c>
+      <c r="O74" t="n">
+        <v>100</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.1015312579119225</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>10.76307103438327</v>
+      </c>
+      <c r="R74" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0.3034018796604436</v>
+      </c>
+      <c r="V74" t="n">
+        <v>44208.32152267794</v>
+      </c>
+      <c r="W74" t="n">
+        <v>44208.6249245576</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Dsd</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>45835.79189476449</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1650.088508211522</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1650.088508211522</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3.798546289621367</v>
+      </c>
+      <c r="O75" t="n">
+        <v>100</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>10.96884883756443</v>
+      </c>
+      <c r="R75" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>45835.79189476449</v>
+      </c>
+      <c r="W75" t="n">
+        <v>45835.79189476449</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.03276740300332791</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-175.766800185349</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Dsd</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J76" t="n">
+        <v>43404.33691784277</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.3774473713006101</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1562.178681671039</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1562.55612904234</v>
+      </c>
+      <c r="N76" t="n">
+        <v>3.597044495953821</v>
+      </c>
+      <c r="O76" t="n">
+        <v>100</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.4587402519561243</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>10.76307103438327</v>
+      </c>
+      <c r="R76" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U76" t="n">
+        <v>10.48464920279472</v>
+      </c>
+      <c r="V76" t="n">
+        <v>43393.85226863998</v>
+      </c>
+      <c r="W76" t="n">
+        <v>43404.33691784277</v>
+      </c>
+      <c r="X76" t="n">
+        <v>-1.099574710898502</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>87.9626794360986</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Dwa</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J77" t="n">
+        <v>7144.365396895075</v>
+      </c>
+      <c r="K77" t="n">
+        <v>45.77796783732368</v>
+      </c>
+      <c r="L77" t="n">
+        <v>211.419186450899</v>
+      </c>
+      <c r="M77" t="n">
+        <v>257.1971542882227</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.5920744804056691</v>
+      </c>
+      <c r="O77" t="n">
+        <v>100</v>
+      </c>
+      <c r="P77" t="n">
+        <v>2.939075235736398</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>3.384448726751575</v>
+      </c>
+      <c r="R77" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S77" t="n">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1271.610217703435</v>
+      </c>
+      <c r="V77" t="n">
+        <v>5872.755179191639</v>
+      </c>
+      <c r="W77" t="n">
+        <v>7144.365396895075</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Dwa</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>7110.534082881402</v>
+      </c>
+      <c r="K78" t="n">
+        <v>15.48818841876066</v>
+      </c>
+      <c r="L78" t="n">
+        <v>240.4910385649698</v>
+      </c>
+      <c r="M78" t="n">
+        <v>255.9792269837305</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.5892707803492875</v>
+      </c>
+      <c r="O78" t="n">
+        <v>100</v>
+      </c>
+      <c r="P78" t="n">
+        <v>1.264701339930059</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>3.387261269014822</v>
+      </c>
+      <c r="R78" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U78" t="n">
+        <v>430.2274560766851</v>
+      </c>
+      <c r="V78" t="n">
+        <v>6680.306626804717</v>
+      </c>
+      <c r="W78" t="n">
+        <v>7110.534082881402</v>
+      </c>
+      <c r="X78" t="n">
+        <v>90.86933825568904</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>-87.21555634221238</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Dwa</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J79" t="n">
+        <v>7400.724993726148</v>
+      </c>
+      <c r="K79" t="n">
+        <v>64.2887933580697</v>
+      </c>
+      <c r="L79" t="n">
+        <v>202.1373064160716</v>
+      </c>
+      <c r="M79" t="n">
+        <v>266.4260997741413</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.613319750861283</v>
+      </c>
+      <c r="O79" t="n">
+        <v>100</v>
+      </c>
+      <c r="P79" t="n">
+        <v>3.176315298327816</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>3.387261269014822</v>
+      </c>
+      <c r="R79" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1785.799815501936</v>
+      </c>
+      <c r="V79" t="n">
+        <v>5614.925178224212</v>
+      </c>
+      <c r="W79" t="n">
+        <v>7400.724993726148</v>
+      </c>
+      <c r="X79" t="n">
+        <v>-55.53247656223805</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>27.84564010448219</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Dwb</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J80" t="n">
+        <v>15418.73403788782</v>
+      </c>
+      <c r="K80" t="n">
+        <v>2.794748513095711</v>
+      </c>
+      <c r="L80" t="n">
+        <v>552.2796768508658</v>
+      </c>
+      <c r="M80" t="n">
+        <v>555.0744253639616</v>
+      </c>
+      <c r="N80" t="n">
+        <v>1.277795638498991</v>
+      </c>
+      <c r="O80" t="n">
+        <v>100</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1.284116074234018</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>5.669429904096891</v>
+      </c>
+      <c r="R80" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S80" t="n">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U80" t="n">
+        <v>77.63190314154754</v>
+      </c>
+      <c r="V80" t="n">
+        <v>15341.10213474627</v>
+      </c>
+      <c r="W80" t="n">
+        <v>15418.73403788782</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Dwb</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J81" t="n">
+        <v>16358.29439671598</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.1236622479158053</v>
+      </c>
+      <c r="L81" t="n">
+        <v>588.7749360338596</v>
+      </c>
+      <c r="M81" t="n">
+        <v>588.8985982817754</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1.355659756633921</v>
+      </c>
+      <c r="O81" t="n">
+        <v>100</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.3298718481419703</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>5.676604599662018</v>
+      </c>
+      <c r="R81" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S81" t="n">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U81" t="n">
+        <v>3.435062442105703</v>
+      </c>
+      <c r="V81" t="n">
+        <v>16354.85933427388</v>
+      </c>
+      <c r="W81" t="n">
+        <v>16358.29439671598</v>
+      </c>
+      <c r="X81" t="n">
+        <v>8.01325879553972</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>-109.4857775489813</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Dwb</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J82" t="n">
+        <v>15062.03622537691</v>
+      </c>
+      <c r="K82" t="n">
+        <v>6.560204290987798</v>
+      </c>
+      <c r="L82" t="n">
+        <v>535.673099822581</v>
+      </c>
+      <c r="M82" t="n">
+        <v>542.2333041135687</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1.248235046301954</v>
+      </c>
+      <c r="O82" t="n">
+        <v>100</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1.584882916336106</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>5.676604599662018</v>
+      </c>
+      <c r="R82" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S82" t="n">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U82" t="n">
+        <v>182.2278969718833</v>
+      </c>
+      <c r="V82" t="n">
+        <v>14879.80832840503</v>
+      </c>
+      <c r="W82" t="n">
+        <v>15062.03622537691</v>
+      </c>
+      <c r="X82" t="n">
+        <v>-11.29636733367626</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>49.81973108485454</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Dwc</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J83" t="n">
+        <v>28723.51710927258</v>
+      </c>
+      <c r="K83" t="n">
+        <v>8.424300368351492</v>
+      </c>
+      <c r="L83" t="n">
+        <v>1025.622315565462</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1034.046615933813</v>
+      </c>
+      <c r="N83" t="n">
+        <v>2.380401970381706</v>
+      </c>
+      <c r="O83" t="n">
+        <v>100</v>
+      </c>
+      <c r="P83" t="n">
+        <v>1.646738877678486</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>8.077348070249256</v>
+      </c>
+      <c r="R83" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S83" t="n">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U83" t="n">
+        <v>234.0083435653193</v>
+      </c>
+      <c r="V83" t="n">
+        <v>28489.50876570727</v>
+      </c>
+      <c r="W83" t="n">
+        <v>28723.51710927258</v>
+      </c>
+      <c r="X83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Dwc</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J84" t="n">
+        <v>30604.64454098391</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.03449509203324197</v>
+      </c>
+      <c r="L84" t="n">
+        <v>1101.732708383387</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1101.767203475421</v>
+      </c>
+      <c r="N84" t="n">
+        <v>2.536296508921319</v>
+      </c>
+      <c r="O84" t="n">
+        <v>100</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0.1888962775213365</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>8.096762187343</v>
+      </c>
+      <c r="R84" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S84" t="n">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0.958197000923388</v>
+      </c>
+      <c r="V84" t="n">
+        <v>30603.68634398299</v>
+      </c>
+      <c r="W84" t="n">
+        <v>30604.64454098391</v>
+      </c>
+      <c r="X84" t="n">
+        <v>25.16941582895475</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>-228.3311784537777</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Dwc</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J85" t="n">
+        <v>27941.32394066979</v>
+      </c>
+      <c r="K85" t="n">
+        <v>17.31365019177881</v>
+      </c>
+      <c r="L85" t="n">
+        <v>988.5740116723338</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1005.887661864112</v>
+      </c>
+      <c r="N85" t="n">
+        <v>2.315579332099706</v>
+      </c>
+      <c r="O85" t="n">
+        <v>100</v>
+      </c>
+      <c r="P85" t="n">
+        <v>2.224062163600135</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>8.096762187343</v>
+      </c>
+      <c r="R85" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S85" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U85" t="n">
+        <v>480.9347275494113</v>
+      </c>
+      <c r="V85" t="n">
+        <v>27460.38921312038</v>
+      </c>
+      <c r="W85" t="n">
+        <v>27941.32394066979</v>
+      </c>
+      <c r="X85" t="n">
+        <v>-26.66804947028194</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>111.1449116793834</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Dwd</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J86" t="n">
+        <v>44256.84894997126</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.006271059408059349</v>
+      </c>
+      <c r="L86" t="n">
+        <v>1593.240291139557</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1593.246562198965</v>
+      </c>
+      <c r="N86" t="n">
+        <v>3.667694664362259</v>
+      </c>
+      <c r="O86" t="n">
+        <v>100</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0.08552004210291329</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>10.90133317811028</v>
+      </c>
+      <c r="R86" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S86" t="n">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0.1741960946683153</v>
+      </c>
+      <c r="V86" t="n">
+        <v>44256.67475387659</v>
+      </c>
+      <c r="W86" t="n">
+        <v>44256.84894997126</v>
+      </c>
+      <c r="X86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Dwd</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J87" t="n">
+        <v>46170.72360595036</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>1662.146049814213</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1662.146049814213</v>
+      </c>
+      <c r="N87" t="n">
+        <v>3.826303061266604</v>
+      </c>
+      <c r="O87" t="n">
+        <v>100</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>10.90133317811028</v>
+      </c>
+      <c r="R87" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S87" t="n">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" t="n">
+        <v>46170.72360595036</v>
+      </c>
+      <c r="W87" t="n">
+        <v>46170.72360595036</v>
+      </c>
+      <c r="X87" t="n">
+        <v>0.01881317822417805</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>-206.7172760239673</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Dwd</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J88" t="n">
+        <v>43290.92691611594</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.1487397196821734</v>
+      </c>
+      <c r="L88" t="n">
+        <v>1558.324629260492</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1558.473368980174</v>
+      </c>
+      <c r="N88" t="n">
+        <v>3.587645877026183</v>
+      </c>
+      <c r="O88" t="n">
+        <v>100</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0.5068580897590497</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>10.90133317811028</v>
+      </c>
+      <c r="R88" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S88" t="n">
+        <v>1</v>
+      </c>
+      <c r="T88" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U88" t="n">
+        <v>4.131658880060371</v>
+      </c>
+      <c r="V88" t="n">
+        <v>43286.79525723588</v>
+      </c>
+      <c r="W88" t="n">
+        <v>43290.92691611594</v>
+      </c>
+      <c r="X88" t="n">
+        <v>-0.427405980822342</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>104.7469856371972</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>EF</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J89" t="n">
+        <v>85649.5239261637</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>3083.382861341894</v>
+      </c>
+      <c r="M89" t="n">
+        <v>3083.382861341894</v>
+      </c>
+      <c r="N89" t="n">
+        <v>7.098026844709699</v>
+      </c>
+      <c r="O89" t="n">
+        <v>100</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>12.91323609531377</v>
+      </c>
+      <c r="R89" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S89" t="n">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" t="n">
+        <v>85649.5239261637</v>
+      </c>
+      <c r="W89" t="n">
+        <v>85649.5239261637</v>
+      </c>
+      <c r="X89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>EF</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J90" t="n">
+        <v>87137.211486538</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>3136.939613515368</v>
+      </c>
+      <c r="M90" t="n">
+        <v>3136.939613515368</v>
+      </c>
+      <c r="N90" t="n">
+        <v>7.22131586905011</v>
+      </c>
+      <c r="O90" t="n">
+        <v>100</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>12.91323609531377</v>
+      </c>
+      <c r="R90" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S90" t="n">
+        <v>1</v>
+      </c>
+      <c r="T90" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" t="n">
+        <v>87137.211486538</v>
+      </c>
+      <c r="W90" t="n">
+        <v>87137.211486538</v>
+      </c>
+      <c r="X90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>-160.6702565204228</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>EF</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J91" t="n">
+        <v>84833.11891830213</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>3053.992281058877</v>
+      </c>
+      <c r="M91" t="n">
+        <v>3053.992281058877</v>
+      </c>
+      <c r="N91" t="n">
+        <v>7.03036897113001</v>
+      </c>
+      <c r="O91" t="n">
+        <v>100</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>12.91323609531377</v>
+      </c>
+      <c r="R91" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1</v>
+      </c>
+      <c r="T91" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" t="n">
+        <v>84833.11891830213</v>
+      </c>
+      <c r="W91" t="n">
+        <v>84833.11891830213</v>
+      </c>
+      <c r="X91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>88.171740849049</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>对比基准</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J92" t="n">
+        <v>10614.68249864975</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.02166460283545347</v>
+      </c>
+      <c r="L92" t="n">
+        <v>382.1069053485556</v>
+      </c>
+      <c r="M92" t="n">
+        <v>382.1285699513911</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0.8796698203300898</v>
+      </c>
+      <c r="O92" t="n">
+        <v>100</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0.2447959017897887</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>3.288421182203374</v>
+      </c>
+      <c r="R92" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S92" t="n">
+        <v>1</v>
+      </c>
+      <c r="T92" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0.6017945232070409</v>
+      </c>
+      <c r="V92" t="n">
+        <v>10614.08070412654</v>
+      </c>
+      <c r="W92" t="n">
+        <v>10614.68249864975</v>
+      </c>
+      <c r="X92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>辐射制冷</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J93" t="n">
+        <v>11734.24111363903</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>422.4326800910052</v>
+      </c>
+      <c r="M93" t="n">
+        <v>422.4326800910052</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0.9724509210198095</v>
+      </c>
+      <c r="O93" t="n">
+        <v>100</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>3.291991728977802</v>
+      </c>
+      <c r="R93" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S93" t="n">
+        <v>1</v>
+      </c>
+      <c r="T93" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" t="n">
+        <v>11734.24111363903</v>
+      </c>
+      <c r="W93" t="n">
+        <v>11734.24111363903</v>
+      </c>
+      <c r="X93" t="n">
+        <v>0.06499380850636041</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>-120.977324227349</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>辐射制热/保温</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J94" t="n">
+        <v>10137.10397047537</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.3389299430185526</v>
+      </c>
+      <c r="L94" t="n">
+        <v>364.5968129940946</v>
+      </c>
+      <c r="M94" t="n">
+        <v>364.9357429371132</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0.8400914892659143</v>
+      </c>
+      <c r="O94" t="n">
+        <v>100</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0.7384139348839754</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>3.291991728977802</v>
+      </c>
+      <c r="R94" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="S94" t="n">
+        <v>1</v>
+      </c>
+      <c r="T94" t="n">
+        <v>2896</v>
+      </c>
+      <c r="U94" t="n">
+        <v>9.414720639404239</v>
+      </c>
+      <c r="V94" t="n">
+        <v>10127.68924983596</v>
+      </c>
+      <c r="W94" t="n">
+        <v>10137.10397047537</v>
+      </c>
+      <c r="X94" t="n">
+        <v>-0.9517960205492975</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>52.53027706338298</v>
       </c>
     </row>
   </sheetData>
